--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488072_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488072_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.1208</v>
+        <v>-1.3879</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5453</v>
+        <v>-0.9528</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5755</v>
+        <v>-0.4351</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2454</v>
@@ -610,13 +610,13 @@
         <v>0.3964</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2808</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3047</v>
+        <v>-0.1027</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5855</v>
+        <v>-0.4451</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.2326</v>
+        <v>-1.612</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4281</v>
+        <v>1.0206</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.6607</v>
+        <v>-2.6326</v>
       </c>
       <c r="G3" t="n">
         <v>0.9011</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8476</v>
+        <v>-1.227</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0586</v>
+        <v>-0.4661</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.789</v>
+        <v>-0.7609</v>
       </c>
       <c r="V3" t="n">
         <v>-2.8719</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.7073</v>
+        <v>-1.7001</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.3466</v>
+        <v>-5.1429</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6393</v>
+        <v>3.4427</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8027</v>
@@ -766,13 +766,13 @@
         <v>3.3698</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.8454</v>
+        <v>-1.8382</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9873</v>
+        <v>-0.7836</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8581</v>
+        <v>-1.0546</v>
       </c>
       <c r="V4" t="n">
         <v>0.5532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.9274</v>
+        <v>-1.9836</v>
       </c>
       <c r="E5" t="n">
         <v>-1.1005</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8269</v>
+        <v>-0.8831</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6896</v>
@@ -844,13 +844,13 @@
         <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.436</v>
+        <v>-1.4922</v>
       </c>
       <c r="T5" t="n">
         <v>-0.6864</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7497</v>
+        <v>-0.8058</v>
       </c>
       <c r="V5" t="n">
         <v>0.6036</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0151</v>
+        <v>-4.0047</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1373</v>
+        <v>-1.2391</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.8779</v>
+        <v>-2.7655</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5166</v>
@@ -922,13 +922,13 @@
         <v>2.7751</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1349</v>
+        <v>-2.1244</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9322</v>
+        <v>-1.034</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2027</v>
+        <v>-1.0904</v>
       </c>
       <c r="V6" t="n">
         <v>-2.1476</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VIDALES MOLINA</t>
+          <t>A. AGUILAR GARCIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.4485</v>
+        <v>-4.1283</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.5288</v>
+        <v>-3.7117</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0803</v>
+        <v>-0.4167</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6071</v>
+        <v>-2.7809</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.1328</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5019</v>
+        <v>-2.9138</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2965</v>
+        <v>-1.2166</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6911</v>
+        <v>0.7806</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3945</v>
+        <v>-1.9972</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9037</v>
+        <v>-1.5643</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7964</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1073</v>
+        <v>-0.9166</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.9556</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>3.568</v>
+        <v>3.1716</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.1259</v>
+        <v>-2.8036</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8698</v>
+        <v>-1.5039</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2562</v>
+        <v>-1.2997</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3278</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3278</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. AGUILAR GARCIA</t>
+          <t>J. HERMOSO PINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.7709</v>
+        <v>-4.8989</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0173</v>
+        <v>-2.057</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7536</v>
+        <v>-2.8419</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7809</v>
+        <v>-2.746</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1328</v>
+        <v>-2.2141</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9138</v>
+        <v>-0.5319</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2166</v>
+        <v>-0.5379</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7806</v>
+        <v>-0.5379</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9972</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5643</v>
+        <v>-2.2081</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.6762</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9166</v>
+        <v>-0.5319</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1716</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-3.4461</v>
+        <v>-0.9369</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.8095</v>
+        <v>-0.7946</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.6366</v>
+        <v>-0.1423</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-1.8107</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HERMOSO PINO</t>
+          <t>R. VIDALES MOLINA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.0746</v>
+        <v>-5.4103</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2608</v>
+        <v>-4.7325</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8138</v>
+        <v>-0.6778</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.746</v>
+        <v>-0.6071</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2141</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5319</v>
+        <v>-1.5019</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5379</v>
+        <v>1.2965</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5379</v>
+        <v>2.6911</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.3945</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2081</v>
+        <v>-1.9037</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6762</v>
+        <v>-1.7964</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5319</v>
+        <v>-0.1073</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>-4.9556</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>3.568</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1126</v>
+        <v>-2.0878</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9984</v>
+        <v>-1.0735</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1142</v>
+        <v>-1.0143</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8107</v>
+        <v>-1.3278</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.0772</v>
+        <v>-1.3278</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.5909</v>
+        <v>-9.2363</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.1047</v>
+        <v>-6.0028</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.4862</v>
+        <v>-3.2335</v>
       </c>
       <c r="G10" t="n">
         <v>-3.6755</v>
@@ -1234,13 +1234,13 @@
         <v>2.5769</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.0545</v>
+        <v>-2.6999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.4241</v>
+        <v>-1.3222</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6304</v>
+        <v>-1.3777</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4645</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.7668</v>
+        <v>-10.2928</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.353199999999999</v>
+        <v>-8.047599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4137</v>
+        <v>-2.2452</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9456</v>
@@ -1312,13 +1312,13 @@
         <v>2.1805</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2443</v>
+        <v>-1.7702</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3103</v>
+        <v>-1.0047</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.7655</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8107</v>
@@ -1348,7 +1348,7 @@
         <v>-44.6549</v>
       </c>
       <c r="E12" t="n">
-        <v>-31.9664</v>
+        <v>-31.9663</v>
       </c>
       <c r="F12" t="n">
         <v>-12.6887</v>
@@ -1393,10 +1393,10 @@
         <v>-17.5281</v>
       </c>
       <c r="T12" t="n">
-        <v>-8.7719</v>
+        <v>-8.771699999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.756399999999999</v>
+        <v>-8.7563</v>
       </c>
       <c r="V12" t="n">
         <v>-12.0007</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8619</v>
+        <v>11.6233</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8404</v>
+        <v>6.8591</v>
       </c>
       <c r="F13" t="n">
-        <v>5.0215</v>
+        <v>4.7642</v>
       </c>
       <c r="G13" t="n">
         <v>6.9177</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3823</v>
+        <v>2.1437</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0441</v>
+        <v>1.0628</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3382</v>
+        <v>1.0809</v>
       </c>
       <c r="V13" t="n">
         <v>3.3547</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.242000000000001</v>
+        <v>7.9733</v>
       </c>
       <c r="E14" t="n">
-        <v>5.3959</v>
+        <v>4.5809</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8462</v>
+        <v>3.3923</v>
       </c>
       <c r="G14" t="n">
         <v>4.0999</v>
@@ -1546,13 +1546,13 @@
         <v>1.784</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0977</v>
+        <v>1.8289</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4024</v>
+        <v>0.5874</v>
       </c>
       <c r="U14" t="n">
-        <v>1.6953</v>
+        <v>1.2415</v>
       </c>
       <c r="V14" t="n">
         <v>4.2249</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5847</v>
+        <v>4.7699</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5305</v>
+        <v>0.8733</v>
       </c>
       <c r="F15" t="n">
-        <v>4.0542</v>
+        <v>3.8966</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.6748</v>
+        <v>3.0409</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.2436</v>
+        <v>0.284</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5687</v>
+        <v>2.757</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9059</v>
+        <v>2.8178</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.7898</v>
+        <v>0.2023</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8839</v>
+        <v>2.6154</v>
       </c>
       <c r="M15" t="n">
-        <v>0.231</v>
+        <v>0.2232</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4538</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6848</v>
+        <v>0.1415</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3876</v>
+        <v>-1.784</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1893</v>
+        <v>-4.1627</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5769</v>
+        <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>6.0019</v>
+        <v>2.9798</v>
       </c>
       <c r="T15" t="n">
-        <v>4.152</v>
+        <v>1.6851</v>
       </c>
       <c r="U15" t="n">
-        <v>1.8499</v>
+        <v>1.2947</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8701</v>
+        <v>0.5331</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4737</v>
+        <v>0.5331</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1184</v>
+        <v>4.1758</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6883</v>
+        <v>2.8475</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4301</v>
+        <v>1.3283</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0409</v>
+        <v>1.8713</v>
       </c>
       <c r="H16" t="n">
-        <v>0.284</v>
+        <v>1.1595</v>
       </c>
       <c r="I16" t="n">
-        <v>2.757</v>
+        <v>0.7118</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8178</v>
+        <v>1.1629</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2023</v>
+        <v>1.2717</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6154</v>
+        <v>-0.1089</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2232</v>
+        <v>0.7084</v>
       </c>
       <c r="N16" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.1123</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1415</v>
+        <v>0.8207</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.1627</v>
+        <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3787</v>
+        <v>1.3876</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3283</v>
+        <v>1.0379</v>
       </c>
       <c r="T16" t="n">
-        <v>2.5</v>
+        <v>0.5985</v>
       </c>
       <c r="U16" t="n">
-        <v>1.8282</v>
+        <v>0.4395</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5331</v>
+        <v>0.8701</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5331</v>
+        <v>2.0772</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.586</v>
+        <v>4.1046</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4826</v>
+        <v>0.1004</v>
       </c>
       <c r="F17" t="n">
-        <v>3.1034</v>
+        <v>4.0041</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1092</v>
+        <v>-0.4253</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4262</v>
+        <v>-0.6378</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.2126</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1388</v>
+        <v>-0.5825</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8139999999999999</v>
+        <v>-0.5177</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6752</v>
+        <v>-0.0648</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9704</v>
+        <v>0.1572</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3879</v>
+        <v>-0.1201</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3583</v>
+        <v>0.2774</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7929</v>
+        <v>2.7751</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="R17" t="n">
-        <v>1.784</v>
+        <v>2.9733</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0804</v>
+        <v>1.7547</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0683</v>
+        <v>0.8811</v>
       </c>
       <c r="U17" t="n">
-        <v>0.012</v>
+        <v>0.8736</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6353</v>
+        <v>3.9857</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0325</v>
+        <v>0.4931</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6028</v>
+        <v>3.4927</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8713</v>
+        <v>-1.6748</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1595</v>
+        <v>-3.2436</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7118</v>
+        <v>1.5687</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1629</v>
+        <v>-1.9059</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2717</v>
+        <v>-2.7898</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1089</v>
+        <v>0.8839</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7084</v>
+        <v>0.231</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1123</v>
+        <v>-0.4538</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8207</v>
+        <v>0.6848</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-1.1893</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3876</v>
+        <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5024999999999999</v>
+        <v>3.4029</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2165</v>
+        <v>2.1146</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.286</v>
+        <v>1.2883</v>
       </c>
       <c r="V18" t="n">
         <v>0.8701</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0772</v>
+        <v>1.4737</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5452</v>
+        <v>3.4756</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.122</v>
+        <v>-0.1286</v>
       </c>
       <c r="F19" t="n">
-        <v>3.6672</v>
+        <v>3.6043</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4253</v>
+        <v>1.1092</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6378</v>
+        <v>0.4262</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2126</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5825</v>
+        <v>0.1388</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5177</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0648</v>
+        <v>-0.6752</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1572</v>
+        <v>0.9704</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1201</v>
+        <v>-0.3879</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2774</v>
+        <v>1.3583</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9733</v>
+        <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1953</v>
+        <v>0.97</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3413</v>
+        <v>0.4571</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5366</v>
+        <v>0.5129</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5221</v>
+        <v>3.0321</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0312</v>
+        <v>0.3216</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4909</v>
+        <v>2.7105</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1576</v>
+        <v>-0.2949</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.5168</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7831</v>
+        <v>0.2219</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4039</v>
+        <v>-1.0692</v>
       </c>
       <c r="K20" t="n">
-        <v>0.034</v>
+        <v>-0.4704</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3699</v>
+        <v>-0.5988</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2463</v>
+        <v>0.7743</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6595</v>
+        <v>-0.0463</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4132</v>
+        <v>0.8207</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1982</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1805</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5627</v>
+        <v>0.9039</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8077</v>
+        <v>0.3553</v>
       </c>
       <c r="U20" t="n">
-        <v>0.755</v>
+        <v>0.5486</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.0178</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1061</v>
+        <v>2.7187</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1878</v>
+        <v>0.0312</v>
       </c>
       <c r="F21" t="n">
-        <v>2.2939</v>
+        <v>2.6875</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2949</v>
+        <v>1.1576</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5168</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2219</v>
+        <v>1.7831</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.0692</v>
+        <v>1.4039</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4704</v>
+        <v>0.034</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5988</v>
+        <v>1.3699</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7743</v>
+        <v>-0.2463</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0463</v>
+        <v>-0.6595</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8207</v>
+        <v>0.4132</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5947</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9822</v>
+        <v>-2.1805</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0221</v>
+        <v>1.7593</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1541</v>
+        <v>0.8077</v>
       </c>
       <c r="U21" t="n">
-        <v>0.132</v>
+        <v>0.9516</v>
       </c>
       <c r="V21" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>3.0178</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7036</v>
+        <v>1.1391</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0568</v>
+        <v>0.3507</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7604</v>
+        <v>0.7884</v>
       </c>
       <c r="G22" t="n">
         <v>1.9765</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3197</v>
+        <v>0.7552</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2275</v>
+        <v>0.18</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5472</v>
+        <v>0.5753</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7997</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.1922</v>
+        <v>0.1905</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5145</v>
+        <v>-0.4126</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3224</v>
+        <v>0.6031</v>
       </c>
       <c r="G26" t="n">
         <v>-0.8713</v>
@@ -2482,13 +2482,13 @@
         <v>0.7929</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.1138</v>
+        <v>0.2689</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1651</v>
+        <v>-0.0633</v>
       </c>
       <c r="U26" t="n">
-        <v>0.0514</v>
+        <v>0.3322</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,10 +2515,10 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.9661</v>
+        <v>-2.7624</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.3395</v>
+        <v>-4.1358</v>
       </c>
       <c r="F27" t="n">
         <v>1.3733</v>
@@ -2560,10 +2560,10 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>0.1982</v>
+        <v>0.402</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1138</v>
+        <v>0.09</v>
       </c>
       <c r="U27" t="n">
         <v>0.312</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>44.65510000000001</v>
+        <v>45.3343</v>
       </c>
       <c r="E28" t="n">
         <v>12.6889</v>
       </c>
       <c r="F28" t="n">
-        <v>31.9663</v>
+        <v>32.6453</v>
       </c>
       <c r="G28" t="n">
-        <v>17.1085</v>
+        <v>17.10850000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>2.367200000000001</v>
+        <v>2.367200000000002</v>
       </c>
       <c r="I28" t="n">
         <v>14.7414</v>
@@ -2614,10 +2614,10 @@
         <v>14.1192</v>
       </c>
       <c r="K28" t="n">
-        <v>6.2261</v>
+        <v>6.226099999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>7.8929</v>
+        <v>7.892899999999998</v>
       </c>
       <c r="M28" t="n">
         <v>2.9894</v>
@@ -2629,7 +2629,7 @@
         <v>6.8485</v>
       </c>
       <c r="P28" t="n">
-        <v>-1.982299999999999</v>
+        <v>-1.9823</v>
       </c>
       <c r="Q28" t="n">
         <v>-23.7867</v>
@@ -2638,13 +2638,13 @@
         <v>21.8045</v>
       </c>
       <c r="S28" t="n">
-        <v>17.5281</v>
+        <v>18.2072</v>
       </c>
       <c r="T28" t="n">
-        <v>8.7562</v>
+        <v>8.7563</v>
       </c>
       <c r="U28" t="n">
-        <v>8.771799999999999</v>
+        <v>9.4511</v>
       </c>
       <c r="V28" t="n">
         <v>12.0006</v>
